--- a/docs/verify/sample_materials.xlsx
+++ b/docs/verify/sample_materials.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="88">
   <si>
     <t>船 名</t>
   </si>
@@ -73,19 +73,16 @@
     <t>備　　考</t>
   </si>
   <si>
-    <t>大竹</t>
-  </si>
-  <si>
     <t>豊島</t>
   </si>
   <si>
     <t>鈴木</t>
   </si>
   <si>
-    <t>木内</t>
+    <t>大竹</t>
   </si>
   <si>
-    <t/>
+    <t>木内</t>
   </si>
   <si>
     <t>材　　　　料　　　　持　　　　出　　　　表</t>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>W1/4(40)</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>モノタロウ</t>
@@ -832,7 +832,7 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -890,13 +890,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -906,7 +906,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -916,50 +916,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -2355,7 +2355,7 @@
       <c r="X26" s="9"/>
       <c r="Y26" s="10"/>
       <c r="Z26" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
@@ -2363,7 +2363,7 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
@@ -2374,7 +2374,7 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
@@ -2931,7 +2931,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="12">
-        <v>0.25</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -2971,7 +2971,7 @@
       <c r="AI3" s="9"/>
       <c r="AJ3" s="10"/>
       <c r="AK3" s="12">
-        <v>0.041666666666666664</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="9"/>
       <c r="AM3" s="9"/>
@@ -3003,7 +3003,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
       <c r="G4" s="12">
-        <v>0.041666666666666664</v>
+        <v>0</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -3019,7 +3019,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="10"/>
       <c r="S4" s="12">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
@@ -3027,7 +3027,7 @@
       <c r="W4" s="9"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="12">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="Z4" s="9"/>
       <c r="AA4" s="9"/>
@@ -3075,7 +3075,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
       <c r="G5" s="12">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -3091,7 +3091,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="10"/>
       <c r="S5" s="12">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
@@ -3099,7 +3099,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="12">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
@@ -3115,7 +3115,7 @@
       <c r="AI5" s="9"/>
       <c r="AJ5" s="10"/>
       <c r="AK5" s="12">
-        <v>0</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="AL5" s="9"/>
       <c r="AM5" s="9"/>
@@ -3210,63 +3210,47 @@
       <c r="BB6" s="5"/>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>20</v>
-      </c>
+      <c r="A7" s="14"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="12">
-        <v>0</v>
-      </c>
+      <c r="G7" s="12"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="13">
-        <f>(G7*24)*7000</f>
-      </c>
+      <c r="M7" s="13"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
       <c r="R7" s="10"/>
-      <c r="S7" s="12">
-        <v>0</v>
-      </c>
+      <c r="S7" s="12"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
       <c r="X7" s="10"/>
-      <c r="Y7" s="12">
-        <v>0</v>
-      </c>
+      <c r="Y7" s="12"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9"/>
       <c r="AD7" s="10"/>
-      <c r="AE7" s="13">
-        <f>(S7*24+Y7*24)*8400</f>
-      </c>
+      <c r="AE7" s="13"/>
       <c r="AF7" s="9"/>
       <c r="AG7" s="9"/>
       <c r="AH7" s="9"/>
       <c r="AI7" s="9"/>
       <c r="AJ7" s="10"/>
-      <c r="AK7" s="12">
-        <v>0</v>
-      </c>
+      <c r="AK7" s="12"/>
       <c r="AL7" s="9"/>
       <c r="AM7" s="9"/>
       <c r="AN7" s="10"/>
-      <c r="AO7" s="13">
-        <f>(AK7*24)*5600</f>
-      </c>
+      <c r="AO7" s="13"/>
       <c r="AP7" s="9"/>
       <c r="AQ7" s="9"/>
       <c r="AR7" s="9"/>
@@ -3282,63 +3266,47 @@
       <c r="BB7" s="5"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8" s="14"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
+      <c r="G8" s="15"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="13">
-        <f>(G8*24)*7000</f>
-      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="10"/>
-      <c r="S8" s="15">
-        <v>0</v>
-      </c>
+      <c r="S8" s="15"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="5"/>
-      <c r="Y8" s="15">
-        <v>0</v>
-      </c>
+      <c r="Y8" s="15"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="5"/>
-      <c r="AE8" s="13">
-        <f>(S8*24+Y8*24)*8400</f>
-      </c>
+      <c r="AE8" s="13"/>
       <c r="AF8" s="9"/>
       <c r="AG8" s="9"/>
       <c r="AH8" s="9"/>
       <c r="AI8" s="9"/>
       <c r="AJ8" s="10"/>
-      <c r="AK8" s="15">
-        <v>0</v>
-      </c>
+      <c r="AK8" s="15"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="5"/>
-      <c r="AO8" s="13">
-        <f>(AK8*24)*5600</f>
-      </c>
+      <c r="AO8" s="13"/>
       <c r="AP8" s="9"/>
       <c r="AQ8" s="9"/>
       <c r="AR8" s="9"/>
@@ -3354,63 +3322,47 @@
       <c r="BB8" s="5"/>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>20</v>
-      </c>
+      <c r="A9" s="14"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="15">
-        <v>0</v>
-      </c>
+      <c r="G9" s="15"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="13">
-        <f>(G9*24)*7000</f>
-      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="15">
-        <v>0</v>
-      </c>
+      <c r="S9" s="15"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="5"/>
-      <c r="Y9" s="15">
-        <v>0</v>
-      </c>
+      <c r="Y9" s="15"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="5"/>
-      <c r="AE9" s="13">
-        <f>(S9*24+Y9*24)*8400</f>
-      </c>
+      <c r="AE9" s="13"/>
       <c r="AF9" s="9"/>
       <c r="AG9" s="9"/>
       <c r="AH9" s="9"/>
       <c r="AI9" s="9"/>
       <c r="AJ9" s="10"/>
-      <c r="AK9" s="15">
-        <v>0</v>
-      </c>
+      <c r="AK9" s="15"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
       <c r="AN9" s="5"/>
-      <c r="AO9" s="13">
-        <f>(AK9*24)*5600</f>
-      </c>
+      <c r="AO9" s="13"/>
       <c r="AP9" s="9"/>
       <c r="AQ9" s="9"/>
       <c r="AR9" s="9"/>
@@ -3427,7 +3379,7 @@
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -3485,13 +3437,13 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="5"/>
       <c r="E11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -3501,7 +3453,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="5"/>
       <c r="M11" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -3511,50 +3463,50 @@
       <c r="S11" s="4"/>
       <c r="T11" s="5"/>
       <c r="U11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V11" s="4"/>
       <c r="W11" s="5"/>
       <c r="X11" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="5"/>
       <c r="AB11" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="5"/>
       <c r="AF11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="5"/>
       <c r="AO11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="5"/>
       <c r="AS11" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AT11" s="4"/>
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="5"/>
       <c r="AX11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AY11" s="4"/>
       <c r="AZ11" s="4"/>
@@ -3569,7 +3521,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="5"/>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -3579,7 +3531,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="5"/>
       <c r="M12" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -3589,7 +3541,7 @@
       <c r="S12" s="4"/>
       <c r="T12" s="5"/>
       <c r="U12" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V12" s="4"/>
       <c r="W12" s="5"/>
@@ -3634,7 +3586,7 @@
       <c r="AV12" s="4"/>
       <c r="AW12" s="5"/>
       <c r="AX12" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY12" s="4"/>
       <c r="AZ12" s="4"/>
@@ -3688,7 +3640,7 @@
         <v>40</v>
       </c>
       <c r="AF13" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
@@ -3701,7 +3653,7 @@
       <c r="AM13" s="4"/>
       <c r="AN13" s="5"/>
       <c r="AO13" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
@@ -3714,7 +3666,7 @@
       <c r="AV13" s="4"/>
       <c r="AW13" s="5"/>
       <c r="AX13" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY13" s="4"/>
       <c r="AZ13" s="4"/>
@@ -3749,7 +3701,7 @@
       <c r="S14" s="4"/>
       <c r="T14" s="5"/>
       <c r="U14" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="5"/>
@@ -3874,7 +3826,7 @@
       <c r="AV15" s="4"/>
       <c r="AW15" s="5"/>
       <c r="AX15" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY15" s="4"/>
       <c r="AZ15" s="4"/>
@@ -3909,7 +3861,7 @@
       <c r="S16" s="4"/>
       <c r="T16" s="5"/>
       <c r="U16" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="5"/>
@@ -3954,7 +3906,7 @@
       <c r="AV16" s="4"/>
       <c r="AW16" s="5"/>
       <c r="AX16" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY16" s="4"/>
       <c r="AZ16" s="4"/>
@@ -3989,7 +3941,7 @@
       <c r="S17" s="4"/>
       <c r="T17" s="5"/>
       <c r="U17" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="5"/>
@@ -4014,7 +3966,7 @@
       <c r="AH17" s="4"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="20">
-        <v>952.7</v>
+        <f>SUM(AF17*AB17)</f>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
@@ -4094,7 +4046,7 @@
       <c r="AH18" s="4"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="20">
-        <v>136.3</v>
+        <f>SUM(AF18*AB18)</f>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
@@ -4114,7 +4066,7 @@
       <c r="AV18" s="4"/>
       <c r="AW18" s="5"/>
       <c r="AX18" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY18" s="4"/>
       <c r="AZ18" s="4"/>
@@ -4149,7 +4101,7 @@
       <c r="S19" s="4"/>
       <c r="T19" s="5"/>
       <c r="U19" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="5"/>
@@ -4174,7 +4126,7 @@
       <c r="AH19" s="4"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="20">
-        <v>154.5</v>
+        <f>SUM(AF19*AB19)</f>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
@@ -4194,7 +4146,7 @@
       <c r="AV19" s="4"/>
       <c r="AW19" s="5"/>
       <c r="AX19" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY19" s="4"/>
       <c r="AZ19" s="4"/>
@@ -4229,7 +4181,7 @@
       <c r="S20" s="9"/>
       <c r="T20" s="10"/>
       <c r="U20" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V20" s="9"/>
       <c r="W20" s="10"/>
@@ -4274,7 +4226,7 @@
       <c r="AV20" s="4"/>
       <c r="AW20" s="5"/>
       <c r="AX20" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY20" s="4"/>
       <c r="AZ20" s="4"/>
@@ -4354,7 +4306,7 @@
       <c r="AV21" s="4"/>
       <c r="AW21" s="5"/>
       <c r="AX21" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY21" s="4"/>
       <c r="AZ21" s="4"/>
@@ -4389,7 +4341,7 @@
       <c r="S22" s="4"/>
       <c r="T22" s="5"/>
       <c r="U22" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="5"/>
@@ -4434,7 +4386,7 @@
       <c r="AV22" s="4"/>
       <c r="AW22" s="5"/>
       <c r="AX22" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY22" s="4"/>
       <c r="AZ22" s="4"/>
@@ -4469,7 +4421,7 @@
       <c r="S23" s="4"/>
       <c r="T23" s="5"/>
       <c r="U23" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="5"/>
@@ -4514,7 +4466,7 @@
       <c r="AV23" s="4"/>
       <c r="AW23" s="5"/>
       <c r="AX23" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY23" s="4"/>
       <c r="AZ23" s="4"/>
@@ -4594,7 +4546,7 @@
       <c r="AV24" s="4"/>
       <c r="AW24" s="5"/>
       <c r="AX24" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY24" s="4"/>
       <c r="AZ24" s="4"/>
@@ -4630,7 +4582,7 @@
       <c r="X25" s="4"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
@@ -4638,7 +4590,7 @@
       <c r="AD25" s="4"/>
       <c r="AE25" s="5"/>
       <c r="AF25" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
@@ -4649,7 +4601,7 @@
       <c r="AM25" s="4"/>
       <c r="AN25" s="5"/>
       <c r="AO25" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
@@ -5099,7 +5051,7 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5157,13 +5109,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -5173,7 +5125,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -5183,50 +5135,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -5261,7 +5213,7 @@
       <c r="S3" s="4"/>
       <c r="T3" s="5"/>
       <c r="U3" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="5"/>
@@ -5306,7 +5258,7 @@
       <c r="AV3" s="4"/>
       <c r="AW3" s="5"/>
       <c r="AX3" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AY3" s="4"/>
       <c r="AZ3" s="4"/>
@@ -5341,7 +5293,7 @@
       <c r="S4" s="9"/>
       <c r="T4" s="10"/>
       <c r="U4" s="8" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="V4" s="9"/>
       <c r="W4" s="10"/>
@@ -6662,7 +6614,7 @@
       <c r="X26" s="9"/>
       <c r="Y26" s="10"/>
       <c r="Z26" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
@@ -6670,7 +6622,7 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
@@ -6681,7 +6633,7 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
@@ -7096,7 +7048,7 @@
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -7154,13 +7106,13 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
       <c r="E2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -7170,7 +7122,7 @@
       <c r="K2" s="9"/>
       <c r="L2" s="10"/>
       <c r="M2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="9"/>
       <c r="O2" s="9"/>
@@ -7180,50 +7132,50 @@
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
       <c r="U2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V2" s="9"/>
       <c r="W2" s="10"/>
       <c r="X2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
       <c r="AB2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC2" s="9"/>
       <c r="AD2" s="9"/>
       <c r="AE2" s="10"/>
       <c r="AF2" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" s="9"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK2" s="9"/>
       <c r="AL2" s="9"/>
       <c r="AM2" s="9"/>
       <c r="AN2" s="10"/>
       <c r="AO2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP2" s="9"/>
       <c r="AQ2" s="9"/>
       <c r="AR2" s="10"/>
       <c r="AS2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AT2" s="9"/>
       <c r="AU2" s="9"/>
       <c r="AV2" s="9"/>
       <c r="AW2" s="10"/>
       <c r="AX2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AY2" s="9"/>
       <c r="AZ2" s="9"/>
@@ -8619,7 +8571,7 @@
       <c r="X26" s="9"/>
       <c r="Y26" s="10"/>
       <c r="Z26" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
@@ -8627,7 +8579,7 @@
       <c r="AD26" s="9"/>
       <c r="AE26" s="10"/>
       <c r="AF26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
@@ -8638,7 +8590,7 @@
       <c r="AM26" s="9"/>
       <c r="AN26" s="10"/>
       <c r="AO26" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>

--- a/docs/verify/sample_materials.xlsx
+++ b/docs/verify/sample_materials.xlsx
@@ -73,16 +73,16 @@
     <t>備　　考</t>
   </si>
   <si>
-    <t>豊島</t>
+    <t>作業者A</t>
   </si>
   <si>
-    <t>鈴木</t>
+    <t>作業者B</t>
   </si>
   <si>
-    <t>大竹</t>
+    <t>作業者C</t>
   </si>
   <si>
-    <t>木内</t>
+    <t>作業者D</t>
   </si>
   <si>
     <t>材　　　　料　　　　持　　　　出　　　　表</t>
@@ -2368,7 +2368,9 @@
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27"/>
+      <c r="AJ26" s="27">
+        <f>SUM(AJ3:AJ25)</f>
+      </c>
       <c r="AK26" s="9"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
@@ -2379,7 +2381,9 @@
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27"/>
+      <c r="AS26" s="27">
+        <f>SUM(AS3:AS25)</f>
+      </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
@@ -2840,7 +2844,7 @@
       <c r="AV1" s="4"/>
       <c r="AW1" s="5"/>
       <c r="AX1" s="7">
-        <v>46044</v>
+        <v>46059</v>
       </c>
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
@@ -4595,7 +4599,9 @@
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="20"/>
+      <c r="AJ25" s="20">
+        <f>SUM(AJ12:AJ24)</f>
+      </c>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
@@ -4606,7 +4612,9 @@
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="5"/>
-      <c r="AS25" s="20"/>
+      <c r="AS25" s="20">
+        <f>SUM(AS12:AS24)</f>
+      </c>
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
@@ -6627,7 +6635,9 @@
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27"/>
+      <c r="AJ26" s="27">
+        <f>SUM(AJ3:AJ25)</f>
+      </c>
       <c r="AK26" s="9"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
@@ -6638,7 +6648,9 @@
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27"/>
+      <c r="AS26" s="27">
+        <f>SUM(AS3:AS25)</f>
+      </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
@@ -8584,7 +8596,9 @@
       <c r="AG26" s="9"/>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10"/>
-      <c r="AJ26" s="27"/>
+      <c r="AJ26" s="27">
+        <f>SUM(AJ3:AJ25)</f>
+      </c>
       <c r="AK26" s="9"/>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9"/>
@@ -8595,7 +8609,9 @@
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="10"/>
-      <c r="AS26" s="27"/>
+      <c r="AS26" s="27">
+        <f>SUM(AS3:AS25)</f>
+      </c>
       <c r="AT26" s="9"/>
       <c r="AU26" s="9"/>
       <c r="AV26" s="9"/>
